--- a/research/traditional_assets/database/data/thailand/thailand_recreation.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_recreation.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0609</v>
+        <v>-0.0359</v>
       </c>
       <c r="E2">
-        <v>-0.208</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="G2">
-        <v>0.4029850746268657</v>
+        <v>0.2877094972067039</v>
       </c>
       <c r="H2">
-        <v>0.4029850746268657</v>
+        <v>0.2877094972067039</v>
       </c>
       <c r="I2">
-        <v>0.1244776119402985</v>
+        <v>0.2505586592178771</v>
       </c>
       <c r="J2">
-        <v>0.0988758335979676</v>
+        <v>0.203161312849162</v>
       </c>
       <c r="K2">
-        <v>0.5600000000000001</v>
+        <v>0.969</v>
       </c>
       <c r="L2">
-        <v>0.1671641791044776</v>
+        <v>0.2706703910614525</v>
       </c>
       <c r="M2">
-        <v>0.422</v>
+        <v>0.397</v>
       </c>
       <c r="N2">
-        <v>0.01098958333333333</v>
+        <v>0.010153452685422</v>
       </c>
       <c r="O2">
-        <v>0.7535714285714284</v>
+        <v>0.4097007223942209</v>
       </c>
       <c r="P2">
-        <v>0.422</v>
+        <v>0.397</v>
       </c>
       <c r="Q2">
-        <v>0.01098958333333333</v>
+        <v>0.010153452685422</v>
       </c>
       <c r="R2">
-        <v>0.7535714285714284</v>
+        <v>0.4097007223942209</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.703</v>
+        <v>1.42</v>
       </c>
       <c r="V2">
-        <v>0.01830729166666667</v>
+        <v>0.03631713554987212</v>
       </c>
       <c r="W2">
-        <v>0.0136919315403423</v>
+        <v>0.03</v>
       </c>
       <c r="X2">
-        <v>0.07224775539651389</v>
+        <v>0.1246237164628839</v>
       </c>
       <c r="Y2">
-        <v>-0.05855582385617158</v>
+        <v>-0.09462371646288392</v>
       </c>
       <c r="Z2">
-        <v>0.08530685001273237</v>
+        <v>0.1133018957495965</v>
       </c>
       <c r="AA2">
-        <v>0.008434785906625707</v>
+        <v>0.02301856188878691</v>
       </c>
       <c r="AB2">
-        <v>0.07224775539651389</v>
+        <v>0.1246237164628839</v>
       </c>
       <c r="AC2">
-        <v>-0.06381296948988818</v>
+        <v>-0.101605154574097</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.703</v>
+        <v>-1.42</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,25 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.0186486988354511</v>
+        <v>-0.03768577494692144</v>
       </c>
       <c r="AK2">
-        <v>-0.0222489476849068</v>
+        <v>-0.04628422425032595</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.224</v>
+        <v>-0.205</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.7567276641550053</v>
+        <v>-1.118110236220472</v>
       </c>
       <c r="AQ2">
-        <v>-1.861607142857143</v>
+        <v>-4.375609756097561</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0609</v>
+        <v>-0.0359</v>
       </c>
       <c r="E3">
-        <v>-0.208</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="G3">
-        <v>0.4029850746268657</v>
+        <v>0.2877094972067039</v>
       </c>
       <c r="H3">
-        <v>0.4029850746268657</v>
+        <v>0.2877094972067039</v>
       </c>
       <c r="I3">
-        <v>0.1244776119402985</v>
+        <v>0.2505586592178771</v>
       </c>
       <c r="J3">
-        <v>0.0988758335979676</v>
+        <v>0.203161312849162</v>
       </c>
       <c r="K3">
-        <v>0.5600000000000001</v>
+        <v>0.969</v>
       </c>
       <c r="L3">
-        <v>0.1671641791044776</v>
+        <v>0.2706703910614525</v>
       </c>
       <c r="M3">
-        <v>0.422</v>
+        <v>0.397</v>
       </c>
       <c r="N3">
-        <v>0.01098958333333333</v>
+        <v>0.010153452685422</v>
       </c>
       <c r="O3">
-        <v>0.7535714285714284</v>
+        <v>0.4097007223942209</v>
       </c>
       <c r="P3">
-        <v>0.422</v>
+        <v>0.397</v>
       </c>
       <c r="Q3">
-        <v>0.01098958333333333</v>
+        <v>0.010153452685422</v>
       </c>
       <c r="R3">
-        <v>0.7535714285714284</v>
+        <v>0.4097007223942209</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,31 +767,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.703</v>
+        <v>1.42</v>
       </c>
       <c r="V3">
-        <v>0.01830729166666667</v>
+        <v>0.03631713554987212</v>
       </c>
       <c r="W3">
-        <v>0.0136919315403423</v>
+        <v>0.03</v>
       </c>
       <c r="X3">
-        <v>0.07224775539651389</v>
+        <v>0.1246237164628839</v>
       </c>
       <c r="Y3">
-        <v>-0.05855582385617158</v>
+        <v>-0.09462371646288392</v>
       </c>
       <c r="Z3">
-        <v>0.08530685001273237</v>
+        <v>0.1133018957495965</v>
       </c>
       <c r="AA3">
-        <v>0.008434785906625707</v>
+        <v>0.02301856188878691</v>
       </c>
       <c r="AB3">
-        <v>0.07224775539651389</v>
+        <v>0.1246237164628839</v>
       </c>
       <c r="AC3">
-        <v>-0.06381296948988818</v>
+        <v>-0.101605154574097</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.703</v>
+        <v>-1.42</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -812,25 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.0186486988354511</v>
+        <v>-0.03768577494692144</v>
       </c>
       <c r="AK3">
-        <v>-0.0222489476849068</v>
+        <v>-0.04628422425032595</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.224</v>
+        <v>-0.205</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.7567276641550053</v>
+        <v>-1.118110236220472</v>
       </c>
       <c r="AQ3">
-        <v>-1.861607142857143</v>
+        <v>-4.375609756097561</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/thailand/thailand_recreation.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_recreation.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0359</v>
+        <v>0.00046</v>
       </c>
       <c r="E2">
-        <v>-0.09300000000000001</v>
+        <v>-0.0475</v>
       </c>
       <c r="G2">
-        <v>0.2877094972067039</v>
+        <v>0.3253796095444685</v>
       </c>
       <c r="H2">
-        <v>0.2877094972067039</v>
+        <v>0.3253796095444685</v>
       </c>
       <c r="I2">
-        <v>0.2505586592178771</v>
+        <v>0.3253796095444685</v>
       </c>
       <c r="J2">
-        <v>0.203161312849162</v>
+        <v>0.2606734371918754</v>
       </c>
       <c r="K2">
-        <v>0.969</v>
+        <v>1.41</v>
       </c>
       <c r="L2">
-        <v>0.2706703910614525</v>
+        <v>0.3058568329718004</v>
       </c>
       <c r="M2">
-        <v>0.397</v>
+        <v>0.622</v>
       </c>
       <c r="N2">
-        <v>0.010153452685422</v>
+        <v>0.01480952380952381</v>
       </c>
       <c r="O2">
-        <v>0.4097007223942209</v>
+        <v>0.4411347517730497</v>
       </c>
       <c r="P2">
-        <v>0.397</v>
+        <v>0.622</v>
       </c>
       <c r="Q2">
-        <v>0.010153452685422</v>
+        <v>0.01480952380952381</v>
       </c>
       <c r="R2">
-        <v>0.4097007223942209</v>
+        <v>0.4411347517730497</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="V2">
-        <v>0.03631713554987212</v>
+        <v>0.03595238095238095</v>
       </c>
       <c r="W2">
-        <v>0.03</v>
+        <v>0.04392523364485981</v>
       </c>
       <c r="X2">
-        <v>0.1246237164628839</v>
+        <v>0.1010277151122006</v>
       </c>
       <c r="Y2">
-        <v>-0.09462371646288392</v>
+        <v>-0.05710248146734082</v>
       </c>
       <c r="Z2">
-        <v>0.1133018957495965</v>
+        <v>0.1502607561929596</v>
       </c>
       <c r="AA2">
-        <v>0.02301856188878691</v>
+        <v>0.03916898779186915</v>
       </c>
       <c r="AB2">
-        <v>0.1246237164628839</v>
+        <v>0.1010277151122006</v>
       </c>
       <c r="AC2">
-        <v>-0.101605154574097</v>
+        <v>-0.06185872732033148</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-1.42</v>
+        <v>-1.51</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,25 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.03768577494692144</v>
+        <v>-0.03729315880464312</v>
       </c>
       <c r="AK2">
-        <v>-0.04628422425032595</v>
+        <v>-0.0466193269527632</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.205</v>
+        <v>-0.219</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-1.118110236220472</v>
+        <v>-0.8162162162162162</v>
       </c>
       <c r="AQ2">
-        <v>-4.375609756097561</v>
+        <v>-6.849315068493151</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0359</v>
+        <v>0.00046</v>
       </c>
       <c r="E3">
-        <v>-0.09300000000000001</v>
+        <v>-0.0475</v>
       </c>
       <c r="G3">
-        <v>0.2877094972067039</v>
+        <v>0.3253796095444685</v>
       </c>
       <c r="H3">
-        <v>0.2877094972067039</v>
+        <v>0.3253796095444685</v>
       </c>
       <c r="I3">
-        <v>0.2505586592178771</v>
+        <v>0.3253796095444685</v>
       </c>
       <c r="J3">
-        <v>0.203161312849162</v>
+        <v>0.2606734371918754</v>
       </c>
       <c r="K3">
-        <v>0.969</v>
+        <v>1.41</v>
       </c>
       <c r="L3">
-        <v>0.2706703910614525</v>
+        <v>0.3058568329718004</v>
       </c>
       <c r="M3">
-        <v>0.397</v>
+        <v>0.622</v>
       </c>
       <c r="N3">
-        <v>0.010153452685422</v>
+        <v>0.01480952380952381</v>
       </c>
       <c r="O3">
-        <v>0.4097007223942209</v>
+        <v>0.4411347517730497</v>
       </c>
       <c r="P3">
-        <v>0.397</v>
+        <v>0.622</v>
       </c>
       <c r="Q3">
-        <v>0.010153452685422</v>
+        <v>0.01480952380952381</v>
       </c>
       <c r="R3">
-        <v>0.4097007223942209</v>
+        <v>0.4411347517730497</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,31 +767,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="V3">
-        <v>0.03631713554987212</v>
+        <v>0.03595238095238095</v>
       </c>
       <c r="W3">
-        <v>0.03</v>
+        <v>0.04392523364485981</v>
       </c>
       <c r="X3">
-        <v>0.1246237164628839</v>
+        <v>0.1010277151122006</v>
       </c>
       <c r="Y3">
-        <v>-0.09462371646288392</v>
+        <v>-0.05710248146734082</v>
       </c>
       <c r="Z3">
-        <v>0.1133018957495965</v>
+        <v>0.1502607561929596</v>
       </c>
       <c r="AA3">
-        <v>0.02301856188878691</v>
+        <v>0.03916898779186915</v>
       </c>
       <c r="AB3">
-        <v>0.1246237164628839</v>
+        <v>0.1010277151122006</v>
       </c>
       <c r="AC3">
-        <v>-0.101605154574097</v>
+        <v>-0.06185872732033148</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-1.42</v>
+        <v>-1.51</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -812,25 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.03768577494692144</v>
+        <v>-0.03729315880464312</v>
       </c>
       <c r="AK3">
-        <v>-0.04628422425032595</v>
+        <v>-0.0466193269527632</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.205</v>
+        <v>-0.219</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-1.118110236220472</v>
+        <v>-0.8162162162162162</v>
       </c>
       <c r="AQ3">
-        <v>-4.375609756097561</v>
+        <v>-6.849315068493151</v>
       </c>
     </row>
   </sheetData>
